--- a/jpcore-r4b/develop/StructureDefinition-JP-Device.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-JP-Device.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-JP-Device.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-JP-Device.xlsx
@@ -413,7 +413,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -433,7 +433,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -663,7 +663,7 @@
     <t>Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
   </si>
   <si>
-    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
+    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](http://hl7.org/fhir/R4B/device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
